--- a/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9705_escuela-basica-salomon-sack_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35932B26-7047-4E92-8EB4-A6E31A403F4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B099B0-84F6-486A-B20C-FE1083200020}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D54813-32F8-4B86-95B1-8670BA579C30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6962282-91EA-4E1F-986E-455A682675C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DC252A5-1FD1-42F4-B805-D829604CB9CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0069C28-8F8E-4146-B0AA-865A2000E4E2}"/>
 </file>